--- a/94/food/tm2026-sm.xlsx
+++ b/94/food/tm2026-sm.xlsx
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C1" s="55" t="inlineStr">
         <is>
-          <t>МБОУ "СОШ с.Старый-Ачхой"</t>
+          <t>МБОУ «СОШ с. Старый-Ачхой»</t>
         </is>
       </c>
       <c r="D1" s="58" t="n"/>

--- a/94/food/tm2026-sm.xlsx
+++ b/94/food/tm2026-sm.xlsx
@@ -6213,8 +6213,8 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C195:D195"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C138:D138"/>

--- a/94/food/tm2026-sm.xlsx
+++ b/94/food/tm2026-sm.xlsx
@@ -6213,8 +6213,8 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C195:D195"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C138:D138"/>
